--- a/Experiments/EnvGen.xlsx
+++ b/Experiments/EnvGen.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="436">
   <si>
     <t>x0</t>
   </si>
@@ -1256,9 +1256,6 @@
     <t>greenstrips</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
     <t>Grid Size (x, y)</t>
   </si>
   <si>
@@ -1268,40 +1265,40 @@
     <t>testwall6</t>
   </si>
   <si>
+    <t>Base Length</t>
+  </si>
+  <si>
+    <t>wallRight</t>
+  </si>
+  <si>
+    <t>testwall8</t>
+  </si>
+  <si>
     <t>bluestrips</t>
   </si>
   <si>
-    <t>Base Length</t>
-  </si>
-  <si>
-    <t>wallRight</t>
-  </si>
-  <si>
-    <t>testwall8</t>
+    <t>deathzone</t>
+  </si>
+  <si>
+    <t>wallBot</t>
+  </si>
+  <si>
+    <t>testwall7</t>
   </si>
   <si>
     <t>blackdots</t>
   </si>
   <si>
-    <t>deathzone</t>
-  </si>
-  <si>
-    <t>wallBot</t>
-  </si>
-  <si>
-    <t>testwall7</t>
+    <t>wallLeft</t>
+  </si>
+  <si>
+    <t>testwall3</t>
   </si>
   <si>
     <t>red</t>
   </si>
   <si>
-    <t>startLocation</t>
-  </si>
-  <si>
-    <t>wallLeft</t>
-  </si>
-  <si>
-    <t>testwall3</t>
+    <t>agentLocation</t>
   </si>
   <si>
     <t>whitedots</t>
@@ -1310,19 +1307,19 @@
     <t>0.8</t>
   </si>
   <si>
-    <t>agentLocation</t>
-  </si>
-  <si>
-    <t>cueInformation</t>
-  </si>
-  <si>
-    <t>cyclinder</t>
-  </si>
-  <si>
-    <t>lengthFlash</t>
-  </si>
-  <si>
-    <t>enableRotation</t>
+    <t>Reward Delay</t>
+  </si>
+  <si>
+    <t>Reward Length</t>
+  </si>
+  <si>
+    <t>Deathzone Action</t>
+  </si>
+  <si>
+    <t>teleportation</t>
+  </si>
+  <si>
+    <t>slow down</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1383,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1407,11 +1404,10 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2248,57 +2244,30 @@
       <c r="A2" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3.0</v>
-      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="1">
-        <v>3.0</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="AC5" s="2">
-        <v>5.0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F6" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -2309,12 +2278,6 @@
       <c r="A8" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -2345,47 +2308,26 @@
       <c r="A14" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="U14" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="AA14" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="M15" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="T15" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="S16" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="R17" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="Q18" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
@@ -2396,67 +2338,31 @@
       <c r="A20" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="AY20" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E21" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="S21" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="V22" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="U23" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="V23" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="W23" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H24" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="V24" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J25" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
@@ -2467,9 +2373,6 @@
       <c r="A27" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="V27" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
@@ -2480,12 +2383,6 @@
       <c r="A29" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D29" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="P29" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
@@ -2531,9 +2428,6 @@
       <c r="A38" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="BT38" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
@@ -2549,9 +2443,6 @@
       <c r="A41" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="M41" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
@@ -2577,9 +2468,6 @@
       <c r="A46" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="K46" s="2">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
@@ -2590,25 +2478,16 @@
       <c r="A48" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="P48" s="2">
-        <v>2.0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G49" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="T50" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
@@ -2634,9 +2513,6 @@
       <c r="A55" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="L55" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
@@ -2647,9 +2523,6 @@
       <c r="A57" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H57" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
@@ -2695,9 +2568,6 @@
       <c r="A66" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="M66" s="2">
-        <v>4.0</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
@@ -2713,15 +2583,6 @@
       <c r="A69" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G69" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L69" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R69" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
@@ -2752,9 +2613,6 @@
       <c r="A75" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E75" s="2">
-        <v>3.0</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
@@ -2879,6 +2737,9 @@
     <row r="100">
       <c r="A100" s="1" t="s">
         <v>299</v>
+      </c>
+      <c r="CD100" s="2">
+        <v>1.0</v>
       </c>
     </row>
     <row r="101">
@@ -3569,7 +3430,7 @@
       <c r="H1" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>410</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -3592,97 +3453,70 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C2" s="3">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D2" s="3">
-        <v>10.0</v>
+        <v>22.0</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>414</v>
+      <c r="F2" s="3">
+        <v>1.0</v>
       </c>
       <c r="G2" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H2" s="3">
         <v>0.0</v>
       </c>
-      <c r="I2" s="2">
-        <v>1.0</v>
+      <c r="I2" s="3">
+        <v>10.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L2" s="4">
-        <v>100.0</v>
+        <v>160.0</v>
       </c>
       <c r="M2" s="4">
-        <v>100.0</v>
+        <v>160.0</v>
       </c>
       <c r="N2" s="2"/>
       <c r="P2" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q2" s="6">
         <v>10.0</v>
       </c>
       <c r="R2" s="6" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="K3" s="4" t="s">
         <v>417</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="L3" s="4">
         <v>1.0</v>
       </c>
       <c r="M3" s="5"/>
       <c r="P3" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="Q3" s="6">
         <v>10.0</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="B4" s="3">
         <v>1.0</v>
@@ -3694,7 +3528,7 @@
         <v>5.0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F4" s="3">
         <v>1.0</v>
@@ -3705,103 +3539,97 @@
       <c r="H4" s="3">
         <v>0.0</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L4" s="4">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="M4" s="5"/>
       <c r="P4" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Q4" s="6">
         <v>10.0</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
       </c>
       <c r="C5" s="3">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F5" s="3">
         <v>1.0</v>
       </c>
       <c r="G5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H5" s="3">
         <v>0.0</v>
       </c>
-      <c r="I5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="L5" s="4">
-        <v>50.0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>50.0</v>
-      </c>
+      <c r="I5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
       <c r="P5" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="Q5" s="6">
         <v>10.0</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
       </c>
       <c r="C6" s="3">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="D6" s="3">
         <v>7.0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1.0</v>
       </c>
       <c r="G6" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H6" s="3">
         <v>0.0</v>
       </c>
-      <c r="I6" s="2">
-        <v>1.0</v>
+      <c r="I6" s="3">
+        <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L6" s="4">
         <v>1.0</v>
@@ -3814,123 +3642,102 @@
       <c r="R6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="K7" s="9" t="s">
+      <c r="A7" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="L7" s="8">
+        <v>100.0</v>
+      </c>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="K8" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="L8" s="8">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="K9" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="P7" s="6" t="s">
+      <c r="L9" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="Q7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="K8" s="9" t="s">
+    </row>
+    <row r="10">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="L8" s="9">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="K9" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="L9" s="9">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="K10" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0.0</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
